--- a/output/pdf_financials_xlsx/VST.xlsx
+++ b/output/pdf_financials_xlsx/VST.xlsx
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>16.849308</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>17.739773</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>36.869673</v>
       </c>
     </row>
     <row r="93">
@@ -3563,7 +3563,11 @@
           <t>Reserve 15</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4539,7 +4543,11 @@
           <t>Reserve 18</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>16.849308</v>
       </c>

--- a/output/pdf_financials_xlsx/VST.xlsx
+++ b/output/pdf_financials_xlsx/VST.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.202377</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.230344</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>16.274992</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.202377</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.230344</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>16.274992</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.379678</v>
+        <v>0.177301</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.482087</v>
+        <v>0.251743</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>19.877277</v>
+        <v>3.602285</v>
       </c>
     </row>
     <row r="49">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08368200000000001</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08368200000000001</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -7172,7 +7172,11 @@
           <t>Cash used for lease payments</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E149" s="5" t="n">
         <v>-0.08368200000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/VST.xlsx
+++ b/output/pdf_financials_xlsx/VST.xlsx
@@ -6986,7 +6986,11 @@
           <t>Cash used for additions to intangible assets</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E143" s="5" t="n">
         <v>-0.208639</v>
       </c>

--- a/output/pdf_financials_xlsx/VST.xlsx
+++ b/output/pdf_financials_xlsx/VST.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-17.389047</v>
+        <v>-17.420006</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>10.625344</v>
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.030959</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-10.080436</v>
+        <v>-0.089196</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.246242</v>
+        <v>0.119249</v>
       </c>
     </row>
     <row r="18">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-17.389047</v>
+        <v>-17.420006</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>10.625344</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-14.556972</v>
+        <v>-14.587931</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>11.317372</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-120.7539400434838</v>
+        <v>-121.0107531519933</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>67.69651472208733</v>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.1777209491202242</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>94.87162015648623</v>
+        <v>0.8394645858054101</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>25.78536663008603</v>
+        <v>12.48722470281727</v>
       </c>
     </row>
     <row r="32">
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003232</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002902</v>
       </c>
     </row>
     <row r="112">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003232</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002902</v>
       </c>
     </row>
     <row r="135">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-3.176414</v>
+        <v>-3.179646</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.503329</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.16671</v>
+        <v>-3.169612</v>
       </c>
     </row>
   </sheetData>
@@ -4917,7 +4917,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>-0.356563</v>
       </c>
@@ -5689,7 +5693,11 @@
           <t>Cash used for purchase of equipment</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>-0.003232</v>
       </c>
@@ -8344,7 +8352,11 @@
           <t>Current income tax recovery (expense) 24</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -9517,7 +9529,11 @@
           <t>Current income tax recovery (expense) 27</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E226" s="5" t="n">
         <v>-0.030959</v>
       </c>
